--- a/assignment3/data/trainingdataset_ontario_budgets_v18_llm_sample.xlsx
+++ b/assignment3/data/trainingdataset_ontario_budgets_v18_llm_sample.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E4E585-84C4-5D4D-BFAB-FBE4379D2427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5140" yWindow="1140" windowWidth="30160" windowHeight="19660" activeTab="1" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
+    <workbookView xWindow="5140" yWindow="1140" windowWidth="30160" windowHeight="19660" xr2:uid="{FB597964-1960-7349-B80F-395C3D8D9DDC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -2730,7 +2730,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -2774,7 +2774,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -3129,7 +3128,7 @@
     <col min="3" max="3" width="14.6640625" customWidth="1"/>
     <col min="4" max="5" width="15" style="13" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="15" style="13" customWidth="1"/>
-    <col min="7" max="7" width="15" style="24" customWidth="1"/>
+    <col min="7" max="7" width="15" style="23" customWidth="1"/>
     <col min="8" max="8" width="15" style="13" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
@@ -3159,7 +3158,7 @@
       <c r="F1" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>394</v>
       </c>
       <c r="H1" s="12" t="s">
@@ -3224,7 +3223,7 @@
       <c r="F2" s="13">
         <v>1</v>
       </c>
-      <c r="G2" s="23">
+      <c r="G2" s="22">
         <v>1</v>
       </c>
       <c r="H2" s="13">
@@ -3271,7 +3270,7 @@
       <c r="F3" s="13">
         <v>1</v>
       </c>
-      <c r="G3" s="23">
+      <c r="G3" s="22">
         <v>1</v>
       </c>
       <c r="H3" s="13">
@@ -3318,7 +3317,7 @@
       <c r="F4" s="13">
         <v>1</v>
       </c>
-      <c r="G4" s="23">
+      <c r="G4" s="22">
         <v>0</v>
       </c>
       <c r="H4" s="20">
@@ -3365,7 +3364,7 @@
       <c r="F5" s="13">
         <v>1</v>
       </c>
-      <c r="G5" s="23">
+      <c r="G5" s="22">
         <v>0</v>
       </c>
       <c r="H5" s="13">
@@ -3412,7 +3411,7 @@
       <c r="F6" s="13">
         <v>1</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <v>1</v>
       </c>
       <c r="H6" s="13">
@@ -3456,7 +3455,7 @@
       <c r="F7" s="13">
         <v>1</v>
       </c>
-      <c r="G7" s="23">
+      <c r="G7" s="22">
         <v>0</v>
       </c>
       <c r="H7" s="13">
@@ -3503,7 +3502,7 @@
       <c r="F8" s="13">
         <v>1</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="22">
         <v>1</v>
       </c>
       <c r="H8" s="13">
@@ -3550,7 +3549,7 @@
       <c r="F9" s="13">
         <v>1</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="22">
         <v>1</v>
       </c>
       <c r="H9" s="13">
@@ -3597,7 +3596,7 @@
       <c r="F10" s="13">
         <v>1</v>
       </c>
-      <c r="G10" s="23">
+      <c r="G10" s="22">
         <v>0</v>
       </c>
       <c r="H10" s="13">
@@ -3644,7 +3643,7 @@
       <c r="F11" s="13">
         <v>1</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="22">
         <v>1</v>
       </c>
       <c r="H11" s="13">
@@ -3688,7 +3687,7 @@
       <c r="F12" s="13">
         <v>1</v>
       </c>
-      <c r="G12" s="23">
+      <c r="G12" s="22">
         <v>0</v>
       </c>
       <c r="H12" s="13">
@@ -3735,7 +3734,7 @@
       <c r="F13" s="13">
         <v>1</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="22">
         <v>1</v>
       </c>
       <c r="H13" s="13">
@@ -3782,7 +3781,7 @@
       <c r="F14" s="13">
         <v>1</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="22">
         <v>1</v>
       </c>
       <c r="H14" s="13">
@@ -3829,7 +3828,7 @@
       <c r="F15" s="13">
         <v>1</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <v>0</v>
       </c>
       <c r="H15" s="13">
@@ -3876,7 +3875,7 @@
       <c r="F16" s="13">
         <v>1</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>0</v>
       </c>
       <c r="H16" s="20">
@@ -3920,7 +3919,7 @@
       <c r="F17" s="13">
         <v>1</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="22">
         <v>0</v>
       </c>
       <c r="H17" s="13">
@@ -3967,7 +3966,7 @@
       <c r="F18" s="13">
         <v>1</v>
       </c>
-      <c r="G18" s="23">
+      <c r="G18" s="22">
         <v>1</v>
       </c>
       <c r="H18" s="13">
@@ -4014,7 +4013,7 @@
       <c r="F19" s="13">
         <v>1</v>
       </c>
-      <c r="G19" s="23">
+      <c r="G19" s="22">
         <v>1</v>
       </c>
       <c r="H19" s="13">
@@ -4061,7 +4060,7 @@
       <c r="F20" s="13">
         <v>1</v>
       </c>
-      <c r="G20" s="23">
+      <c r="G20" s="22">
         <v>0</v>
       </c>
       <c r="H20" s="20">
@@ -4108,7 +4107,7 @@
       <c r="F21" s="13">
         <v>1</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="22">
         <v>0</v>
       </c>
       <c r="H21" s="13">
@@ -4155,7 +4154,7 @@
       <c r="F22" s="13">
         <v>1</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="22">
         <v>0</v>
       </c>
       <c r="H22" s="20">
@@ -4202,7 +4201,7 @@
       <c r="F23" s="13">
         <v>1</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="22">
         <v>1</v>
       </c>
       <c r="H23" s="13">
@@ -4249,7 +4248,7 @@
       <c r="F24" s="13">
         <v>1</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="22">
         <v>1</v>
       </c>
       <c r="H24" s="13">
@@ -4296,7 +4295,7 @@
       <c r="F25" s="13">
         <v>1</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="22">
         <v>1</v>
       </c>
       <c r="H25" s="13">
@@ -4343,7 +4342,7 @@
       <c r="F26" s="13">
         <v>1</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="22">
         <v>0</v>
       </c>
       <c r="H26" s="13">
@@ -4390,7 +4389,7 @@
       <c r="F27" s="13">
         <v>1</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="22">
         <v>1</v>
       </c>
       <c r="H27" s="13">
@@ -4437,7 +4436,7 @@
       <c r="F28" s="13">
         <v>1</v>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="22">
         <v>1</v>
       </c>
       <c r="H28" s="13">
@@ -4484,7 +4483,7 @@
       <c r="F29" s="13">
         <v>1</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="22">
         <v>1</v>
       </c>
       <c r="H29" s="13">
@@ -4531,7 +4530,7 @@
       <c r="F30" s="13">
         <v>1</v>
       </c>
-      <c r="G30" s="23">
+      <c r="G30" s="22">
         <v>0</v>
       </c>
       <c r="H30" s="20">
@@ -4578,7 +4577,7 @@
       <c r="F31" s="13">
         <v>1</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="22">
         <v>0</v>
       </c>
       <c r="H31" s="20">
@@ -4625,7 +4624,7 @@
       <c r="F32" s="13">
         <v>1</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="22">
         <v>0</v>
       </c>
       <c r="H32" s="13">
@@ -4672,7 +4671,7 @@
       <c r="F33" s="13">
         <v>1</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="22">
         <v>1</v>
       </c>
       <c r="H33" s="13">
@@ -4719,7 +4718,7 @@
       <c r="F34" s="13">
         <v>1</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="22">
         <v>1</v>
       </c>
       <c r="H34" s="13">
@@ -4766,7 +4765,7 @@
       <c r="F35" s="13">
         <v>1</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="22">
         <v>1</v>
       </c>
       <c r="H35" s="13">
@@ -4813,7 +4812,7 @@
       <c r="F36" s="13">
         <v>1</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="22">
         <v>0</v>
       </c>
       <c r="H36" s="20">
@@ -4860,7 +4859,7 @@
       <c r="F37" s="13">
         <v>1</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="22">
         <v>1</v>
       </c>
       <c r="H37" s="13">
@@ -4907,7 +4906,7 @@
       <c r="F38" s="13">
         <v>1</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="22">
         <v>0</v>
       </c>
       <c r="H38" s="20">
@@ -4954,7 +4953,7 @@
       <c r="F39" s="13">
         <v>1</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="22">
         <v>0</v>
       </c>
       <c r="H39" s="13">
@@ -5001,7 +5000,7 @@
       <c r="F40" s="13">
         <v>1</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="22">
         <v>1</v>
       </c>
       <c r="H40" s="13">
@@ -5048,7 +5047,7 @@
       <c r="F41" s="13">
         <v>1</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="22">
         <v>1</v>
       </c>
       <c r="H41" s="13">
@@ -5095,7 +5094,7 @@
       <c r="F42" s="13">
         <v>1</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="22">
         <v>1</v>
       </c>
       <c r="H42" s="13">
@@ -5142,7 +5141,7 @@
       <c r="F43" s="13">
         <v>1</v>
       </c>
-      <c r="G43" s="23">
+      <c r="G43" s="22">
         <v>1</v>
       </c>
       <c r="H43" s="13">
@@ -5189,7 +5188,7 @@
       <c r="F44" s="13">
         <v>1</v>
       </c>
-      <c r="G44" s="23">
+      <c r="G44" s="22">
         <v>0</v>
       </c>
       <c r="H44" s="20">
@@ -5236,7 +5235,7 @@
       <c r="F45" s="13">
         <v>1</v>
       </c>
-      <c r="G45" s="23">
+      <c r="G45" s="22">
         <v>0</v>
       </c>
       <c r="H45" s="20">
@@ -5283,7 +5282,7 @@
       <c r="F46" s="13">
         <v>1</v>
       </c>
-      <c r="G46" s="23">
+      <c r="G46" s="22">
         <v>0</v>
       </c>
       <c r="H46" s="13">
@@ -5330,7 +5329,7 @@
       <c r="F47" s="13">
         <v>1</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="22">
         <v>1</v>
       </c>
       <c r="H47" s="13">
@@ -5377,7 +5376,7 @@
       <c r="F48" s="13">
         <v>1</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="22">
         <v>1</v>
       </c>
       <c r="H48" s="13">
@@ -5424,7 +5423,7 @@
       <c r="F49" s="13">
         <v>1</v>
       </c>
-      <c r="G49" s="23">
+      <c r="G49" s="22">
         <v>1</v>
       </c>
       <c r="H49" s="13">
@@ -5471,7 +5470,7 @@
       <c r="F50" s="13">
         <v>1</v>
       </c>
-      <c r="G50" s="23">
+      <c r="G50" s="22">
         <v>1</v>
       </c>
       <c r="H50" s="13">
@@ -5518,7 +5517,7 @@
       <c r="F51" s="13">
         <v>1</v>
       </c>
-      <c r="G51" s="23">
+      <c r="G51" s="22">
         <v>0</v>
       </c>
       <c r="H51" s="20">
@@ -5565,7 +5564,7 @@
       <c r="F52" s="13">
         <v>1</v>
       </c>
-      <c r="G52" s="23">
+      <c r="G52" s="22">
         <v>0</v>
       </c>
       <c r="H52" s="20">
@@ -5612,7 +5611,7 @@
       <c r="F53" s="13">
         <v>1</v>
       </c>
-      <c r="G53" s="23">
+      <c r="G53" s="22">
         <v>0</v>
       </c>
       <c r="H53" s="13">
@@ -5659,7 +5658,7 @@
       <c r="F54" s="13">
         <v>1</v>
       </c>
-      <c r="G54" s="23">
+      <c r="G54" s="22">
         <v>1</v>
       </c>
       <c r="H54" s="13">
@@ -5706,7 +5705,7 @@
       <c r="F55" s="13">
         <v>1</v>
       </c>
-      <c r="G55" s="23">
+      <c r="G55" s="22">
         <v>1</v>
       </c>
       <c r="H55" s="13">
@@ -5753,7 +5752,7 @@
       <c r="F56" s="13">
         <v>1</v>
       </c>
-      <c r="G56" s="23">
+      <c r="G56" s="22">
         <v>1</v>
       </c>
       <c r="H56" s="13">
@@ -5800,7 +5799,7 @@
       <c r="F57" s="13">
         <v>1</v>
       </c>
-      <c r="G57" s="23">
+      <c r="G57" s="22">
         <v>0</v>
       </c>
       <c r="H57" s="13">
@@ -5847,7 +5846,7 @@
       <c r="F58" s="13">
         <v>1</v>
       </c>
-      <c r="G58" s="23">
+      <c r="G58" s="22">
         <v>0</v>
       </c>
       <c r="H58" s="13">
@@ -5891,7 +5890,7 @@
       <c r="F59" s="13">
         <v>1</v>
       </c>
-      <c r="G59" s="23">
+      <c r="G59" s="22">
         <v>0</v>
       </c>
       <c r="H59" s="13">
@@ -5938,7 +5937,7 @@
       <c r="F60" s="13">
         <v>1</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="22">
         <v>0</v>
       </c>
       <c r="H60" s="13">
@@ -5982,7 +5981,7 @@
       <c r="F61" s="13">
         <v>1</v>
       </c>
-      <c r="G61" s="23">
+      <c r="G61" s="22">
         <v>0</v>
       </c>
       <c r="H61" s="20">
@@ -6026,7 +6025,7 @@
       <c r="F62" s="13">
         <v>1</v>
       </c>
-      <c r="G62" s="23">
+      <c r="G62" s="22">
         <v>0</v>
       </c>
       <c r="H62" s="13">
@@ -6073,7 +6072,7 @@
       <c r="F63" s="13">
         <v>1</v>
       </c>
-      <c r="G63" s="23">
+      <c r="G63" s="22">
         <v>0</v>
       </c>
       <c r="H63" s="13">
@@ -6120,7 +6119,7 @@
       <c r="F64" s="13">
         <v>1</v>
       </c>
-      <c r="G64" s="23">
+      <c r="G64" s="22">
         <v>0</v>
       </c>
       <c r="H64" s="20">
@@ -6167,7 +6166,7 @@
       <c r="F65" s="13">
         <v>1</v>
       </c>
-      <c r="G65" s="23">
+      <c r="G65" s="22">
         <v>0</v>
       </c>
       <c r="H65" s="13">
@@ -6214,7 +6213,7 @@
       <c r="F66" s="13">
         <v>1</v>
       </c>
-      <c r="G66" s="23">
+      <c r="G66" s="22">
         <v>0</v>
       </c>
       <c r="H66" s="20">
@@ -6261,7 +6260,7 @@
       <c r="F67" s="13">
         <v>1</v>
       </c>
-      <c r="G67" s="23">
+      <c r="G67" s="22">
         <v>1</v>
       </c>
       <c r="H67" s="13">
@@ -6308,7 +6307,7 @@
       <c r="F68" s="13">
         <v>1</v>
       </c>
-      <c r="G68" s="23">
+      <c r="G68" s="22">
         <v>0</v>
       </c>
       <c r="H68" s="13">
@@ -6355,7 +6354,7 @@
       <c r="F69" s="13">
         <v>1</v>
       </c>
-      <c r="G69" s="23">
+      <c r="G69" s="22">
         <v>0</v>
       </c>
       <c r="H69" s="13">
@@ -6402,7 +6401,7 @@
       <c r="F70" s="13">
         <v>1</v>
       </c>
-      <c r="G70" s="23">
+      <c r="G70" s="22">
         <v>0</v>
       </c>
       <c r="H70" s="13">
@@ -6449,7 +6448,7 @@
       <c r="F71" s="13">
         <v>1</v>
       </c>
-      <c r="G71" s="23">
+      <c r="G71" s="22">
         <v>0</v>
       </c>
       <c r="H71" s="13">
@@ -6493,7 +6492,7 @@
       <c r="F72" s="13">
         <v>1</v>
       </c>
-      <c r="G72" s="23">
+      <c r="G72" s="22">
         <v>0</v>
       </c>
       <c r="H72" s="13">
@@ -6537,7 +6536,7 @@
       <c r="F73" s="13">
         <v>1</v>
       </c>
-      <c r="G73" s="23">
+      <c r="G73" s="22">
         <v>0</v>
       </c>
       <c r="H73" s="20">
@@ -6581,7 +6580,7 @@
       <c r="F74" s="13">
         <v>1</v>
       </c>
-      <c r="G74" s="23">
+      <c r="G74" s="22">
         <v>0</v>
       </c>
       <c r="H74" s="13">
@@ -6628,7 +6627,7 @@
       <c r="F75" s="13">
         <v>1</v>
       </c>
-      <c r="G75" s="23">
+      <c r="G75" s="22">
         <v>0</v>
       </c>
       <c r="H75" s="13">
@@ -6675,7 +6674,7 @@
       <c r="F76" s="13">
         <v>1</v>
       </c>
-      <c r="G76" s="23">
+      <c r="G76" s="22">
         <v>0</v>
       </c>
       <c r="H76" s="13">
@@ -6722,7 +6721,7 @@
       <c r="F77" s="13">
         <v>1</v>
       </c>
-      <c r="G77" s="23">
+      <c r="G77" s="22">
         <v>0</v>
       </c>
       <c r="H77" s="13">
@@ -6769,7 +6768,7 @@
       <c r="F78" s="13">
         <v>1</v>
       </c>
-      <c r="G78" s="23">
+      <c r="G78" s="22">
         <v>0</v>
       </c>
       <c r="H78" s="20">
@@ -6816,7 +6815,7 @@
       <c r="F79" s="13">
         <v>1</v>
       </c>
-      <c r="G79" s="23">
+      <c r="G79" s="22">
         <v>1</v>
       </c>
       <c r="H79" s="13">
@@ -6863,7 +6862,7 @@
       <c r="F80" s="13">
         <v>1</v>
       </c>
-      <c r="G80" s="23">
+      <c r="G80" s="22">
         <v>0</v>
       </c>
       <c r="H80" s="13">
@@ -6910,7 +6909,7 @@
       <c r="F81" s="13">
         <v>1</v>
       </c>
-      <c r="G81" s="23">
+      <c r="G81" s="22">
         <v>0</v>
       </c>
       <c r="H81" s="13">
@@ -6957,7 +6956,7 @@
       <c r="F82" s="13">
         <v>1</v>
       </c>
-      <c r="G82" s="23">
+      <c r="G82" s="22">
         <v>0</v>
       </c>
       <c r="H82" s="13">
@@ -7004,7 +7003,7 @@
       <c r="F83" s="13">
         <v>1</v>
       </c>
-      <c r="G83" s="23">
+      <c r="G83" s="22">
         <v>1</v>
       </c>
       <c r="H83" s="13">
@@ -7051,7 +7050,7 @@
       <c r="F84" s="13">
         <v>1</v>
       </c>
-      <c r="G84" s="23">
+      <c r="G84" s="22">
         <v>0</v>
       </c>
       <c r="H84" s="13">
@@ -7098,7 +7097,7 @@
       <c r="F85" s="13">
         <v>1</v>
       </c>
-      <c r="G85" s="23">
+      <c r="G85" s="22">
         <v>0</v>
       </c>
       <c r="H85" s="20">
@@ -7145,7 +7144,7 @@
       <c r="F86" s="13">
         <v>1</v>
       </c>
-      <c r="G86" s="23">
+      <c r="G86" s="22">
         <v>1</v>
       </c>
       <c r="H86" s="13">
@@ -7189,7 +7188,7 @@
       <c r="F87" s="13">
         <v>1</v>
       </c>
-      <c r="G87" s="23">
+      <c r="G87" s="22">
         <v>1</v>
       </c>
       <c r="H87" s="13">
@@ -7233,7 +7232,7 @@
       <c r="F88" s="13">
         <v>1</v>
       </c>
-      <c r="G88" s="23">
+      <c r="G88" s="22">
         <v>0</v>
       </c>
       <c r="H88" s="13">
@@ -7280,7 +7279,7 @@
       <c r="F89" s="13">
         <v>1</v>
       </c>
-      <c r="G89" s="23">
+      <c r="G89" s="22">
         <v>1</v>
       </c>
       <c r="H89" s="13">
@@ -7327,7 +7326,7 @@
       <c r="F90" s="13">
         <v>1</v>
       </c>
-      <c r="G90" s="23">
+      <c r="G90" s="22">
         <v>0</v>
       </c>
       <c r="H90" s="13">
@@ -7374,7 +7373,7 @@
       <c r="F91" s="13">
         <v>1</v>
       </c>
-      <c r="G91" s="23">
+      <c r="G91" s="22">
         <v>0</v>
       </c>
       <c r="H91" s="13">
@@ -7421,7 +7420,7 @@
       <c r="F92" s="13">
         <v>1</v>
       </c>
-      <c r="G92" s="23">
+      <c r="G92" s="22">
         <v>0</v>
       </c>
       <c r="H92" s="13">
@@ -7468,7 +7467,7 @@
       <c r="F93" s="13">
         <v>1</v>
       </c>
-      <c r="G93" s="23">
+      <c r="G93" s="22">
         <v>0</v>
       </c>
       <c r="H93" s="13">
@@ -7515,7 +7514,7 @@
       <c r="F94" s="13">
         <v>1</v>
       </c>
-      <c r="G94" s="23">
+      <c r="G94" s="22">
         <v>1</v>
       </c>
       <c r="H94" s="13">
@@ -7562,7 +7561,7 @@
       <c r="F95" s="13">
         <v>1</v>
       </c>
-      <c r="G95" s="23">
+      <c r="G95" s="22">
         <v>0</v>
       </c>
       <c r="H95" s="13">
@@ -7609,7 +7608,7 @@
       <c r="F96" s="13">
         <v>1</v>
       </c>
-      <c r="G96" s="23">
+      <c r="G96" s="22">
         <v>0</v>
       </c>
       <c r="H96" s="20">
@@ -7656,7 +7655,7 @@
       <c r="F97" s="13">
         <v>1</v>
       </c>
-      <c r="G97" s="23">
+      <c r="G97" s="22">
         <v>1</v>
       </c>
       <c r="H97" s="13">
@@ -7700,7 +7699,7 @@
       <c r="F98" s="13">
         <v>1</v>
       </c>
-      <c r="G98" s="23">
+      <c r="G98" s="22">
         <v>0</v>
       </c>
       <c r="H98" s="13">
@@ -7744,7 +7743,7 @@
       <c r="F99" s="13">
         <v>1</v>
       </c>
-      <c r="G99" s="23">
+      <c r="G99" s="22">
         <v>0</v>
       </c>
       <c r="H99" s="13">
@@ -7791,7 +7790,7 @@
       <c r="F100" s="13">
         <v>1</v>
       </c>
-      <c r="G100" s="23">
+      <c r="G100" s="22">
         <v>0</v>
       </c>
       <c r="H100" s="13">
@@ -7838,7 +7837,7 @@
       <c r="F101" s="13">
         <v>1</v>
       </c>
-      <c r="G101" s="23">
+      <c r="G101" s="22">
         <v>0</v>
       </c>
       <c r="H101" s="13">
@@ -7885,7 +7884,7 @@
       <c r="F102" s="13">
         <v>1</v>
       </c>
-      <c r="G102" s="23">
+      <c r="G102" s="22">
         <v>0</v>
       </c>
       <c r="H102" s="13">
@@ -7932,7 +7931,7 @@
       <c r="F103" s="13">
         <v>1</v>
       </c>
-      <c r="G103" s="23">
+      <c r="G103" s="22">
         <v>0</v>
       </c>
       <c r="H103" s="13">
@@ -7979,7 +7978,7 @@
       <c r="F104" s="13">
         <v>1</v>
       </c>
-      <c r="G104" s="23">
+      <c r="G104" s="22">
         <v>0</v>
       </c>
       <c r="H104" s="20">
@@ -8026,7 +8025,7 @@
       <c r="F105" s="13">
         <v>1</v>
       </c>
-      <c r="G105" s="23">
+      <c r="G105" s="22">
         <v>0</v>
       </c>
       <c r="H105" s="13">
@@ -8073,7 +8072,7 @@
       <c r="F106" s="13">
         <v>1</v>
       </c>
-      <c r="G106" s="23">
+      <c r="G106" s="22">
         <v>0</v>
       </c>
       <c r="H106" s="20">
@@ -8120,7 +8119,7 @@
       <c r="F107" s="13">
         <v>1</v>
       </c>
-      <c r="G107" s="23">
+      <c r="G107" s="22">
         <v>0</v>
       </c>
       <c r="H107" s="13">
@@ -8167,7 +8166,7 @@
       <c r="F108" s="13">
         <v>1</v>
       </c>
-      <c r="G108" s="23">
+      <c r="G108" s="22">
         <v>0</v>
       </c>
       <c r="H108" s="20">
@@ -8214,7 +8213,7 @@
       <c r="F109" s="13">
         <v>1</v>
       </c>
-      <c r="G109" s="23">
+      <c r="G109" s="22">
         <v>1</v>
       </c>
       <c r="H109" s="13">
@@ -8258,7 +8257,7 @@
       <c r="F110" s="13">
         <v>1</v>
       </c>
-      <c r="G110" s="23">
+      <c r="G110" s="22">
         <v>0</v>
       </c>
       <c r="H110" s="13">
@@ -8302,7 +8301,7 @@
       <c r="F111" s="13">
         <v>1</v>
       </c>
-      <c r="G111" s="23">
+      <c r="G111" s="22">
         <v>0</v>
       </c>
       <c r="H111" s="13">
@@ -8349,7 +8348,7 @@
       <c r="F112" s="13">
         <v>1</v>
       </c>
-      <c r="G112" s="23">
+      <c r="G112" s="22">
         <v>0</v>
       </c>
       <c r="H112" s="13">
@@ -8396,7 +8395,7 @@
       <c r="F113" s="13">
         <v>1</v>
       </c>
-      <c r="G113" s="23">
+      <c r="G113" s="22">
         <v>0</v>
       </c>
       <c r="H113" s="13">
@@ -8443,7 +8442,7 @@
       <c r="F114" s="13">
         <v>1</v>
       </c>
-      <c r="G114" s="23">
+      <c r="G114" s="22">
         <v>0</v>
       </c>
       <c r="H114" s="13">
@@ -8490,7 +8489,7 @@
       <c r="F115" s="13">
         <v>1</v>
       </c>
-      <c r="G115" s="23">
+      <c r="G115" s="22">
         <v>1</v>
       </c>
       <c r="H115" s="13">
@@ -8537,7 +8536,7 @@
       <c r="F116" s="13">
         <v>1</v>
       </c>
-      <c r="G116" s="23">
+      <c r="G116" s="22">
         <v>0</v>
       </c>
       <c r="H116" s="13">
@@ -8584,7 +8583,7 @@
       <c r="F117" s="13">
         <v>1</v>
       </c>
-      <c r="G117" s="23">
+      <c r="G117" s="22">
         <v>0</v>
       </c>
       <c r="H117" s="20">
@@ -8631,7 +8630,7 @@
       <c r="F118" s="13">
         <v>1</v>
       </c>
-      <c r="G118" s="23">
+      <c r="G118" s="22">
         <v>0</v>
       </c>
       <c r="H118" s="13">
@@ -8678,7 +8677,7 @@
       <c r="F119" s="13">
         <v>1</v>
       </c>
-      <c r="G119" s="23">
+      <c r="G119" s="22">
         <v>0</v>
       </c>
       <c r="H119" s="13">
@@ -8725,7 +8724,7 @@
       <c r="F120" s="13">
         <v>1</v>
       </c>
-      <c r="G120" s="23">
+      <c r="G120" s="22">
         <v>0</v>
       </c>
       <c r="H120" s="20">
@@ -8772,7 +8771,7 @@
       <c r="F121" s="13">
         <v>1</v>
       </c>
-      <c r="G121" s="23">
+      <c r="G121" s="22">
         <v>0</v>
       </c>
       <c r="H121" s="20">
@@ -8819,7 +8818,7 @@
       <c r="F122" s="13">
         <v>1</v>
       </c>
-      <c r="G122" s="23">
+      <c r="G122" s="22">
         <v>0</v>
       </c>
       <c r="H122" s="13">
@@ -8866,7 +8865,7 @@
       <c r="F123" s="13">
         <v>1</v>
       </c>
-      <c r="G123" s="23">
+      <c r="G123" s="22">
         <v>0</v>
       </c>
       <c r="H123" s="20">
@@ -8913,7 +8912,7 @@
       <c r="F124" s="13">
         <v>1</v>
       </c>
-      <c r="G124" s="23">
+      <c r="G124" s="22">
         <v>1</v>
       </c>
       <c r="H124" s="20">
@@ -8957,7 +8956,7 @@
       <c r="F125" s="13">
         <v>1</v>
       </c>
-      <c r="G125" s="23">
+      <c r="G125" s="22">
         <v>0</v>
       </c>
       <c r="H125" s="13">
@@ -9001,7 +9000,7 @@
       <c r="F126" s="13">
         <v>1</v>
       </c>
-      <c r="G126" s="23">
+      <c r="G126" s="22">
         <v>0</v>
       </c>
       <c r="H126" s="13">
@@ -9048,7 +9047,7 @@
       <c r="F127" s="13">
         <v>1</v>
       </c>
-      <c r="G127" s="23">
+      <c r="G127" s="22">
         <v>0</v>
       </c>
       <c r="H127" s="13">
@@ -9096,7 +9095,7 @@
       <c r="F128" s="13">
         <v>1</v>
       </c>
-      <c r="G128" s="23">
+      <c r="G128" s="22">
         <v>0</v>
       </c>
       <c r="H128" s="13">
@@ -9144,7 +9143,7 @@
       <c r="F129" s="13">
         <v>1</v>
       </c>
-      <c r="G129" s="23">
+      <c r="G129" s="22">
         <v>0</v>
       </c>
       <c r="H129" s="13">
@@ -9192,7 +9191,7 @@
       <c r="F130" s="13">
         <v>1</v>
       </c>
-      <c r="G130" s="23">
+      <c r="G130" s="22">
         <v>0</v>
       </c>
       <c r="H130" s="13">
@@ -9240,7 +9239,7 @@
       <c r="F131" s="13">
         <v>1</v>
       </c>
-      <c r="G131" s="23">
+      <c r="G131" s="22">
         <v>0</v>
       </c>
       <c r="H131" s="13">
@@ -9288,7 +9287,7 @@
       <c r="F132" s="13">
         <v>1</v>
       </c>
-      <c r="G132" s="23">
+      <c r="G132" s="22">
         <v>0</v>
       </c>
       <c r="H132" s="13">
@@ -9336,7 +9335,7 @@
       <c r="F133" s="13">
         <v>1</v>
       </c>
-      <c r="G133" s="23">
+      <c r="G133" s="22">
         <v>0</v>
       </c>
       <c r="H133" s="20">
@@ -9384,7 +9383,7 @@
       <c r="F134" s="13">
         <v>1</v>
       </c>
-      <c r="G134" s="23">
+      <c r="G134" s="22">
         <v>0</v>
       </c>
       <c r="H134" s="20">
@@ -9432,7 +9431,7 @@
       <c r="F135" s="13">
         <v>1</v>
       </c>
-      <c r="G135" s="23">
+      <c r="G135" s="22">
         <v>0</v>
       </c>
       <c r="H135" s="13">
@@ -9480,7 +9479,7 @@
       <c r="F136" s="13">
         <v>1</v>
       </c>
-      <c r="G136" s="23">
+      <c r="G136" s="22">
         <v>1</v>
       </c>
       <c r="H136" s="20">
@@ -9528,7 +9527,7 @@
       <c r="F137" s="13">
         <v>1</v>
       </c>
-      <c r="G137" s="23">
+      <c r="G137" s="22">
         <v>1</v>
       </c>
       <c r="H137" s="20">
@@ -9576,7 +9575,7 @@
       <c r="F138" s="13">
         <v>1</v>
       </c>
-      <c r="G138" s="23">
+      <c r="G138" s="22">
         <v>0</v>
       </c>
       <c r="H138" s="13">
@@ -9624,7 +9623,7 @@
       <c r="F139" s="13">
         <v>1</v>
       </c>
-      <c r="G139" s="23">
+      <c r="G139" s="22">
         <v>0</v>
       </c>
       <c r="H139" s="13">
@@ -9672,7 +9671,7 @@
       <c r="F140" s="13">
         <v>1</v>
       </c>
-      <c r="G140" s="23">
+      <c r="G140" s="22">
         <v>0</v>
       </c>
       <c r="H140" s="13">
@@ -9720,7 +9719,7 @@
       <c r="F141" s="13">
         <v>1</v>
       </c>
-      <c r="G141" s="23">
+      <c r="G141" s="22">
         <v>0</v>
       </c>
       <c r="H141" s="20">
@@ -9768,7 +9767,7 @@
       <c r="F142" s="13">
         <v>1</v>
       </c>
-      <c r="G142" s="23">
+      <c r="G142" s="22">
         <v>1</v>
       </c>
       <c r="H142" s="20">
@@ -9813,7 +9812,7 @@
       <c r="F143" s="13">
         <v>1</v>
       </c>
-      <c r="G143" s="23">
+      <c r="G143" s="22">
         <v>0</v>
       </c>
       <c r="H143" s="13">
@@ -9858,7 +9857,7 @@
       <c r="F144" s="13">
         <v>1</v>
       </c>
-      <c r="G144" s="23">
+      <c r="G144" s="22">
         <v>0</v>
       </c>
       <c r="H144" s="13">
@@ -9903,7 +9902,7 @@
       <c r="F145" s="13">
         <v>1</v>
       </c>
-      <c r="G145" s="23">
+      <c r="G145" s="22">
         <v>0</v>
       </c>
       <c r="H145" s="13">
@@ -9951,7 +9950,7 @@
       <c r="F146" s="13">
         <v>1</v>
       </c>
-      <c r="G146" s="23">
+      <c r="G146" s="22">
         <v>0</v>
       </c>
       <c r="H146" s="13">
@@ -9999,7 +9998,7 @@
       <c r="F147" s="13">
         <v>1</v>
       </c>
-      <c r="G147" s="23">
+      <c r="G147" s="22">
         <v>0</v>
       </c>
       <c r="H147" s="13">
@@ -10047,7 +10046,7 @@
       <c r="F148" s="13">
         <v>1</v>
       </c>
-      <c r="G148" s="23">
+      <c r="G148" s="22">
         <v>0</v>
       </c>
       <c r="H148" s="20">
@@ -10095,7 +10094,7 @@
       <c r="F149" s="13">
         <v>1</v>
       </c>
-      <c r="G149" s="23">
+      <c r="G149" s="22">
         <v>1</v>
       </c>
       <c r="H149" s="13">
@@ -10143,7 +10142,7 @@
       <c r="F150" s="13">
         <v>1</v>
       </c>
-      <c r="G150" s="23">
+      <c r="G150" s="22">
         <v>0</v>
       </c>
       <c r="H150" s="13">
@@ -10191,7 +10190,7 @@
       <c r="F151" s="13">
         <v>1</v>
       </c>
-      <c r="G151" s="23">
+      <c r="G151" s="22">
         <v>0</v>
       </c>
       <c r="H151" s="20">
@@ -10239,7 +10238,7 @@
       <c r="F152" s="13">
         <v>1</v>
       </c>
-      <c r="G152" s="23">
+      <c r="G152" s="22">
         <v>0</v>
       </c>
       <c r="H152" s="13">
@@ -10287,7 +10286,7 @@
       <c r="F153" s="13">
         <v>1</v>
       </c>
-      <c r="G153" s="23">
+      <c r="G153" s="22">
         <v>0</v>
       </c>
       <c r="H153" s="13">
@@ -10335,7 +10334,7 @@
       <c r="F154" s="13">
         <v>1</v>
       </c>
-      <c r="G154" s="23">
+      <c r="G154" s="22">
         <v>0</v>
       </c>
       <c r="H154" s="13">
@@ -10380,7 +10379,7 @@
       <c r="F155" s="13">
         <v>1</v>
       </c>
-      <c r="G155" s="23">
+      <c r="G155" s="22">
         <v>0</v>
       </c>
       <c r="H155" s="13">
@@ -10428,7 +10427,7 @@
       <c r="F156" s="13">
         <v>1</v>
       </c>
-      <c r="G156" s="23">
+      <c r="G156" s="22">
         <v>0</v>
       </c>
       <c r="H156" s="20">
@@ -10476,7 +10475,7 @@
       <c r="F157" s="13">
         <v>1</v>
       </c>
-      <c r="G157" s="23">
+      <c r="G157" s="22">
         <v>0</v>
       </c>
       <c r="H157" s="13">
@@ -10524,7 +10523,7 @@
       <c r="F158" s="13">
         <v>1</v>
       </c>
-      <c r="G158" s="23">
+      <c r="G158" s="22">
         <v>0</v>
       </c>
       <c r="H158" s="13">
@@ -10572,7 +10571,7 @@
       <c r="F159" s="13">
         <v>1</v>
       </c>
-      <c r="G159" s="23">
+      <c r="G159" s="22">
         <v>0</v>
       </c>
       <c r="H159" s="20">
@@ -10620,7 +10619,7 @@
       <c r="F160" s="13">
         <v>1</v>
       </c>
-      <c r="G160" s="23">
+      <c r="G160" s="22">
         <v>0</v>
       </c>
       <c r="H160" s="20">
@@ -10668,7 +10667,7 @@
       <c r="F161" s="13">
         <v>1</v>
       </c>
-      <c r="G161" s="23">
+      <c r="G161" s="22">
         <v>1</v>
       </c>
       <c r="H161" s="13">
@@ -10713,7 +10712,7 @@
       <c r="F162" s="13">
         <v>1</v>
       </c>
-      <c r="G162" s="23">
+      <c r="G162" s="22">
         <v>0</v>
       </c>
       <c r="H162" s="13">
@@ -10758,7 +10757,7 @@
       <c r="F163" s="13">
         <v>1</v>
       </c>
-      <c r="G163" s="23">
+      <c r="G163" s="22">
         <v>0</v>
       </c>
       <c r="H163" s="13">
@@ -10803,7 +10802,7 @@
       <c r="F164" s="13">
         <v>1</v>
       </c>
-      <c r="G164" s="23">
+      <c r="G164" s="22">
         <v>0</v>
       </c>
       <c r="H164" s="13">
@@ -10848,7 +10847,7 @@
       <c r="F165" s="13">
         <v>1</v>
       </c>
-      <c r="G165" s="23">
+      <c r="G165" s="22">
         <v>0</v>
       </c>
       <c r="H165" s="13">
@@ -10893,7 +10892,7 @@
       <c r="F166" s="13">
         <v>1</v>
       </c>
-      <c r="G166" s="23">
+      <c r="G166" s="22">
         <v>0</v>
       </c>
       <c r="H166" s="13">
@@ -10938,7 +10937,7 @@
       <c r="F167" s="13">
         <v>1</v>
       </c>
-      <c r="G167" s="23">
+      <c r="G167" s="22">
         <v>0</v>
       </c>
       <c r="H167" s="13">
@@ -10986,7 +10985,7 @@
       <c r="F168" s="13">
         <v>1</v>
       </c>
-      <c r="G168" s="23">
+      <c r="G168" s="22">
         <v>1</v>
       </c>
       <c r="H168" s="20">
@@ -11034,7 +11033,7 @@
       <c r="F169" s="13">
         <v>1</v>
       </c>
-      <c r="G169" s="23">
+      <c r="G169" s="22">
         <v>0</v>
       </c>
       <c r="H169" s="13">
@@ -11082,7 +11081,7 @@
       <c r="F170" s="13">
         <v>1</v>
       </c>
-      <c r="G170" s="23">
+      <c r="G170" s="22">
         <v>0</v>
       </c>
       <c r="H170" s="13">
@@ -11130,7 +11129,7 @@
       <c r="F171" s="13">
         <v>1</v>
       </c>
-      <c r="G171" s="23">
+      <c r="G171" s="22">
         <v>0</v>
       </c>
       <c r="H171" s="13">
@@ -11178,7 +11177,7 @@
       <c r="F172" s="13">
         <v>1</v>
       </c>
-      <c r="G172" s="23">
+      <c r="G172" s="22">
         <v>0</v>
       </c>
       <c r="H172" s="13">
@@ -11226,7 +11225,7 @@
       <c r="F173" s="13">
         <v>1</v>
       </c>
-      <c r="G173" s="23">
+      <c r="G173" s="22">
         <v>0</v>
       </c>
       <c r="H173" s="13">
@@ -11274,7 +11273,7 @@
       <c r="F174" s="13">
         <v>1</v>
       </c>
-      <c r="G174" s="23">
+      <c r="G174" s="22">
         <v>0</v>
       </c>
       <c r="H174" s="20">
@@ -11322,7 +11321,7 @@
       <c r="F175" s="13">
         <v>1</v>
       </c>
-      <c r="G175" s="23">
+      <c r="G175" s="22">
         <v>1</v>
       </c>
       <c r="H175" s="13">
@@ -11370,7 +11369,7 @@
       <c r="F176" s="13">
         <v>1</v>
       </c>
-      <c r="G176" s="23">
+      <c r="G176" s="22">
         <v>0</v>
       </c>
       <c r="H176" s="20">
@@ -11418,7 +11417,7 @@
       <c r="F177" s="13">
         <v>1</v>
       </c>
-      <c r="G177" s="23">
+      <c r="G177" s="22">
         <v>0</v>
       </c>
       <c r="H177" s="13">
@@ -11466,7 +11465,7 @@
       <c r="F178" s="13">
         <v>1</v>
       </c>
-      <c r="G178" s="23">
+      <c r="G178" s="22">
         <v>0</v>
       </c>
       <c r="H178" s="13">
@@ -11514,7 +11513,7 @@
       <c r="F179" s="13">
         <v>1</v>
       </c>
-      <c r="G179" s="23">
+      <c r="G179" s="22">
         <v>0</v>
       </c>
       <c r="H179" s="13">
@@ -11562,7 +11561,7 @@
       <c r="F180" s="13">
         <v>1</v>
       </c>
-      <c r="G180" s="23">
+      <c r="G180" s="22">
         <v>0</v>
       </c>
       <c r="H180" s="13">
@@ -11610,7 +11609,7 @@
       <c r="F181" s="13">
         <v>1</v>
       </c>
-      <c r="G181" s="23">
+      <c r="G181" s="22">
         <v>0</v>
       </c>
       <c r="H181" s="13">
@@ -11658,7 +11657,7 @@
       <c r="F182" s="13">
         <v>1</v>
       </c>
-      <c r="G182" s="23">
+      <c r="G182" s="22">
         <v>1</v>
       </c>
       <c r="H182" s="20">
@@ -11703,7 +11702,7 @@
       <c r="F183" s="13">
         <v>1</v>
       </c>
-      <c r="G183" s="23">
+      <c r="G183" s="22">
         <v>0</v>
       </c>
       <c r="H183" s="13">
@@ -11748,7 +11747,7 @@
       <c r="F184" s="13">
         <v>1</v>
       </c>
-      <c r="G184" s="23">
+      <c r="G184" s="22">
         <v>0</v>
       </c>
       <c r="H184" s="13">
@@ -11793,7 +11792,7 @@
       <c r="F185" s="13">
         <v>1</v>
       </c>
-      <c r="G185" s="23">
+      <c r="G185" s="22">
         <v>0</v>
       </c>
       <c r="H185" s="13">
@@ -11838,7 +11837,7 @@
       <c r="F186" s="13">
         <v>1</v>
       </c>
-      <c r="G186" s="24">
+      <c r="G186" s="23">
         <v>0</v>
       </c>
       <c r="H186" s="13">
@@ -11882,7 +11881,7 @@
       <c r="F187" s="13">
         <v>1</v>
       </c>
-      <c r="G187" s="24">
+      <c r="G187" s="23">
         <v>0</v>
       </c>
       <c r="I187" s="4">
@@ -11920,7 +11919,7 @@
       <c r="F188" s="13">
         <v>1</v>
       </c>
-      <c r="G188" s="24">
+      <c r="G188" s="23">
         <v>1</v>
       </c>
       <c r="I188" s="4">
@@ -11958,7 +11957,7 @@
       <c r="F189" s="13">
         <v>1</v>
       </c>
-      <c r="G189" s="24">
+      <c r="G189" s="23">
         <v>1</v>
       </c>
       <c r="I189" s="4">
@@ -11996,7 +11995,7 @@
       <c r="F190" s="13">
         <v>1</v>
       </c>
-      <c r="G190" s="24">
+      <c r="G190" s="23">
         <v>0</v>
       </c>
       <c r="I190" s="4">
@@ -12037,7 +12036,7 @@
       <c r="F191" s="13">
         <v>1</v>
       </c>
-      <c r="G191" s="24">
+      <c r="G191" s="23">
         <v>1</v>
       </c>
       <c r="I191" s="4">
@@ -12078,7 +12077,7 @@
       <c r="F192" s="13">
         <v>1</v>
       </c>
-      <c r="G192" s="24">
+      <c r="G192" s="23">
         <v>0</v>
       </c>
       <c r="I192" s="4">
@@ -12122,7 +12121,7 @@
       <c r="F193" s="13">
         <v>1</v>
       </c>
-      <c r="G193" s="24">
+      <c r="G193" s="23">
         <v>1</v>
       </c>
       <c r="I193" s="4">
@@ -12166,7 +12165,7 @@
       <c r="F194" s="13">
         <v>1</v>
       </c>
-      <c r="G194" s="24">
+      <c r="G194" s="23">
         <v>1</v>
       </c>
       <c r="I194" s="4">
@@ -12210,7 +12209,7 @@
       <c r="F195" s="13">
         <v>1</v>
       </c>
-      <c r="G195" s="24">
+      <c r="G195" s="23">
         <v>1</v>
       </c>
       <c r="I195" s="4">
@@ -12254,7 +12253,7 @@
       <c r="F196" s="13">
         <v>1</v>
       </c>
-      <c r="G196" s="24">
+      <c r="G196" s="23">
         <v>1</v>
       </c>
       <c r="I196" s="4">
@@ -12298,7 +12297,7 @@
       <c r="F197" s="13">
         <v>1</v>
       </c>
-      <c r="G197" s="24">
+      <c r="G197" s="23">
         <v>1</v>
       </c>
       <c r="I197" s="4">
@@ -12342,7 +12341,7 @@
       <c r="F198" s="13">
         <v>1</v>
       </c>
-      <c r="G198" s="24">
+      <c r="G198" s="23">
         <v>1</v>
       </c>
       <c r="I198" s="4">
@@ -12386,7 +12385,7 @@
       <c r="F199" s="13">
         <v>1</v>
       </c>
-      <c r="G199" s="24">
+      <c r="G199" s="23">
         <v>1</v>
       </c>
       <c r="I199" s="4">
@@ -12430,7 +12429,7 @@
       <c r="F200" s="13">
         <v>1</v>
       </c>
-      <c r="G200" s="24">
+      <c r="G200" s="23">
         <v>1</v>
       </c>
       <c r="I200" s="4">
@@ -12474,7 +12473,7 @@
       <c r="F201" s="13">
         <v>1</v>
       </c>
-      <c r="G201" s="24">
+      <c r="G201" s="23">
         <v>1</v>
       </c>
       <c r="I201" s="4">
@@ -12518,7 +12517,7 @@
       <c r="F202" s="13">
         <v>1</v>
       </c>
-      <c r="G202" s="24">
+      <c r="G202" s="23">
         <v>1</v>
       </c>
       <c r="I202" s="4">
@@ -12562,7 +12561,7 @@
       <c r="F203" s="13">
         <v>1</v>
       </c>
-      <c r="G203" s="24">
+      <c r="G203" s="23">
         <v>1</v>
       </c>
       <c r="I203" s="4">
@@ -12606,7 +12605,7 @@
       <c r="F204" s="13">
         <v>1</v>
       </c>
-      <c r="G204" s="24">
+      <c r="G204" s="23">
         <v>1</v>
       </c>
       <c r="I204" s="4">
@@ -12647,7 +12646,7 @@
       <c r="F205" s="13">
         <v>1</v>
       </c>
-      <c r="G205" s="24">
+      <c r="G205" s="23">
         <v>1</v>
       </c>
       <c r="I205" s="4">
@@ -12691,7 +12690,7 @@
       <c r="F206" s="13">
         <v>1</v>
       </c>
-      <c r="G206" s="24">
+      <c r="G206" s="23">
         <v>1</v>
       </c>
       <c r="I206" s="4">
@@ -12735,7 +12734,7 @@
       <c r="F207" s="13">
         <v>1</v>
       </c>
-      <c r="G207" s="24">
+      <c r="G207" s="23">
         <v>0</v>
       </c>
       <c r="I207" s="4">
@@ -12779,7 +12778,7 @@
       <c r="F208" s="13">
         <v>1</v>
       </c>
-      <c r="G208" s="24">
+      <c r="G208" s="23">
         <v>0</v>
       </c>
       <c r="I208" s="4">
@@ -12823,7 +12822,7 @@
       <c r="F209" s="13">
         <v>1</v>
       </c>
-      <c r="G209" s="24">
+      <c r="G209" s="23">
         <v>0</v>
       </c>
       <c r="I209" s="4">
@@ -12867,7 +12866,7 @@
       <c r="F210" s="13">
         <v>1</v>
       </c>
-      <c r="G210" s="24">
+      <c r="G210" s="23">
         <v>1</v>
       </c>
       <c r="I210" s="4">
@@ -12911,7 +12910,7 @@
       <c r="F211" s="13">
         <v>1</v>
       </c>
-      <c r="G211" s="24">
+      <c r="G211" s="23">
         <v>0</v>
       </c>
       <c r="I211" s="4">
@@ -12952,7 +12951,7 @@
       <c r="F212" s="13">
         <v>1</v>
       </c>
-      <c r="G212" s="24">
+      <c r="G212" s="23">
         <v>0</v>
       </c>
       <c r="I212" s="4">
@@ -12996,7 +12995,7 @@
       <c r="F213" s="13">
         <v>1</v>
       </c>
-      <c r="G213" s="24">
+      <c r="G213" s="23">
         <v>0</v>
       </c>
       <c r="I213" s="4">
@@ -13028,13 +13027,13 @@
       <c r="B214" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="C214" s="21" t="s">
+      <c r="C214" t="s">
         <v>480</v>
       </c>
       <c r="F214" s="13">
         <v>1</v>
       </c>
-      <c r="G214" s="24">
+      <c r="G214" s="23">
         <v>0</v>
       </c>
       <c r="I214" s="4">
@@ -13072,7 +13071,7 @@
       <c r="F215" s="13">
         <v>1</v>
       </c>
-      <c r="G215" s="24">
+      <c r="G215" s="23">
         <v>1</v>
       </c>
       <c r="I215" s="4">
@@ -13110,7 +13109,7 @@
       <c r="F216" s="13">
         <v>1</v>
       </c>
-      <c r="G216" s="24">
+      <c r="G216" s="23">
         <v>0</v>
       </c>
       <c r="I216" s="4">
@@ -13148,7 +13147,7 @@
       <c r="F217" s="13">
         <v>1</v>
       </c>
-      <c r="G217" s="24">
+      <c r="G217" s="23">
         <v>0</v>
       </c>
       <c r="I217" s="4">
@@ -13186,7 +13185,7 @@
       <c r="F218" s="13">
         <v>1</v>
       </c>
-      <c r="G218" s="24">
+      <c r="G218" s="23">
         <v>0</v>
       </c>
       <c r="I218" s="4">
@@ -13224,7 +13223,7 @@
       <c r="F219" s="13">
         <v>1</v>
       </c>
-      <c r="G219" s="24">
+      <c r="G219" s="23">
         <v>0</v>
       </c>
       <c r="I219" s="4">
@@ -13262,7 +13261,7 @@
       <c r="F220" s="13">
         <v>1</v>
       </c>
-      <c r="G220" s="24">
+      <c r="G220" s="23">
         <v>1</v>
       </c>
       <c r="I220" s="4">
@@ -13300,7 +13299,7 @@
       <c r="F221" s="13">
         <v>1</v>
       </c>
-      <c r="G221" s="24">
+      <c r="G221" s="23">
         <v>0</v>
       </c>
       <c r="I221" s="4">
@@ -13338,7 +13337,7 @@
       <c r="F222" s="13">
         <v>1</v>
       </c>
-      <c r="G222" s="24">
+      <c r="G222" s="23">
         <v>1</v>
       </c>
       <c r="I222" s="4">
@@ -13376,7 +13375,7 @@
       <c r="F223" s="13">
         <v>1</v>
       </c>
-      <c r="G223" s="24">
+      <c r="G223" s="23">
         <v>1</v>
       </c>
       <c r="I223" s="4">
@@ -13414,7 +13413,7 @@
       <c r="F224" s="13">
         <v>1</v>
       </c>
-      <c r="G224" s="24">
+      <c r="G224" s="23">
         <v>0</v>
       </c>
       <c r="I224" s="4">
@@ -13452,7 +13451,7 @@
       <c r="F225" s="13">
         <v>1</v>
       </c>
-      <c r="G225" s="24">
+      <c r="G225" s="23">
         <v>0</v>
       </c>
       <c r="I225" s="4">
@@ -13490,7 +13489,7 @@
       <c r="F226" s="13">
         <v>1</v>
       </c>
-      <c r="G226" s="24">
+      <c r="G226" s="23">
         <v>1</v>
       </c>
       <c r="I226" s="4">
@@ -13528,7 +13527,7 @@
       <c r="F227" s="13">
         <v>1</v>
       </c>
-      <c r="G227" s="24">
+      <c r="G227" s="23">
         <v>1</v>
       </c>
       <c r="I227" s="4">
@@ -13566,7 +13565,7 @@
       <c r="F228" s="13">
         <v>1</v>
       </c>
-      <c r="G228" s="24">
+      <c r="G228" s="23">
         <v>1</v>
       </c>
       <c r="I228" s="4">
@@ -13604,7 +13603,7 @@
       <c r="F229" s="13">
         <v>1</v>
       </c>
-      <c r="G229" s="24">
+      <c r="G229" s="23">
         <v>1</v>
       </c>
       <c r="I229" s="4">
@@ -13642,7 +13641,7 @@
       <c r="F230" s="13">
         <v>1</v>
       </c>
-      <c r="G230" s="24">
+      <c r="G230" s="23">
         <v>0</v>
       </c>
       <c r="I230" s="4">
@@ -13680,7 +13679,7 @@
       <c r="F231" s="13">
         <v>1</v>
       </c>
-      <c r="G231" s="24">
+      <c r="G231" s="23">
         <v>1</v>
       </c>
       <c r="I231" s="4">
@@ -13718,7 +13717,7 @@
       <c r="F232" s="13">
         <v>1</v>
       </c>
-      <c r="G232" s="24">
+      <c r="G232" s="23">
         <v>1</v>
       </c>
       <c r="I232" s="4">
@@ -13756,7 +13755,7 @@
       <c r="F233" s="13">
         <v>1</v>
       </c>
-      <c r="G233" s="24">
+      <c r="G233" s="23">
         <v>1</v>
       </c>
       <c r="I233" s="4">
@@ -13794,7 +13793,7 @@
       <c r="F234" s="13">
         <v>1</v>
       </c>
-      <c r="G234" s="24">
+      <c r="G234" s="23">
         <v>1</v>
       </c>
       <c r="I234" s="4">
@@ -13832,7 +13831,7 @@
       <c r="F235" s="13">
         <v>1</v>
       </c>
-      <c r="G235" s="24">
+      <c r="G235" s="23">
         <v>0</v>
       </c>
       <c r="I235" s="4">
@@ -13870,7 +13869,7 @@
       <c r="F236" s="13">
         <v>1</v>
       </c>
-      <c r="G236" s="24">
+      <c r="G236" s="23">
         <v>1</v>
       </c>
       <c r="I236" s="4">
@@ -13908,7 +13907,7 @@
       <c r="F237" s="13">
         <v>1</v>
       </c>
-      <c r="G237" s="24">
+      <c r="G237" s="23">
         <v>1</v>
       </c>
       <c r="I237" s="4">
